--- a/MAJSushiConfig/ig/StructureDefinition-fr-patient-history-extension.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-patient-history-extension.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-history-extension</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-history-extension</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -331,7 +331,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-observation-pregnancy-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-observation-contra-indications-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-condition-document|0.1.0|Observation|4.0.1|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-device-auteur-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-administration-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-pregnancy-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-contra-indications-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-condition-document|0.1.0|Observation|4.0.1|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-device-auteur-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-administration-document|0.1.0)
 </t>
   </si>
   <si>
